--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -805,14 +805,16 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1969844</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>03:00 (180.0s)</t>
+        </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -831,7 +833,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00 (180.0s)</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -875,14 +875,16 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>2162007</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>03:00 (180.0s)</t>
+        </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -901,7 +903,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00 (180.0s)</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -945,14 +945,16 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1897370</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>03:00 (180.0s)</t>
+        </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -971,7 +973,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00 (180.0s)</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1015,14 +1015,16 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>2510255</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>03:00 (180.0s)</t>
+        </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1041,7 +1043,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00 (180.0s)</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1085,14 +1085,16 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>1935090</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>03:00 (180.0s)</t>
+        </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1111,7 +1113,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00 (180.0s)</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1155,14 +1155,18 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2.15 MB</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1181,17 +1185,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM / TIER 3</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1. Run main.py backend and open index.html. 2. Submit test features to /predict. 3. Verify API response, latency metrics, and operational health status.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1227,14 +1227,18 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2.33 MB</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1253,17 +1257,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM / TIER 3</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1. Run main.py backend and open index.html. 2. Submit test features to /predict. 3. Verify API response, latency metrics, and operational health status.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1299,14 +1299,18 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2.48 MB</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1325,17 +1329,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM / TIER 3</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1. Run main.py backend and open index.html. 2. Submit test features to /predict. 3. Verify API response, latency metrics, and operational health status.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1371,14 +1371,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1.78 MB</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1401,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1443,14 +1443,18 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2.18 MB</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1469,7 +1473,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1515,11 +1515,13 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1.84 MB</t>
+        </is>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1585,11 +1585,13 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1.31 MB</t>
+        </is>
       </c>
       <c r="H16" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1655,11 +1655,13 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1.79 MB</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1725,11 +1725,13 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1.98 MB</t>
+        </is>
       </c>
       <c r="H18" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1795,11 +1795,13 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2.04 MB</t>
+        </is>
       </c>
       <c r="H19" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1865,11 +1865,13 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1.81 MB</t>
+        </is>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -1935,11 +1935,13 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1.87 MB</t>
+        </is>
       </c>
       <c r="H21" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2005,11 +2005,13 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2.86 MB</t>
+        </is>
       </c>
       <c r="H22" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2075,11 +2075,13 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1.99 MB</t>
+        </is>
       </c>
       <c r="H23" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2145,11 +2145,13 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2.91 MB</t>
+        </is>
       </c>
       <c r="H24" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2215,11 +2215,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1.73 MB</t>
+        </is>
       </c>
       <c r="H25" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2285,11 +2285,13 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2.96 MB</t>
+        </is>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2355,11 +2355,13 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3.03 MB</t>
+        </is>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2425,11 +2425,13 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2.20 MB</t>
+        </is>
       </c>
       <c r="H28" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2495,11 +2495,13 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1.83 MB</t>
+        </is>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2565,11 +2565,13 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1.86 MB</t>
+        </is>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2635,11 +2635,13 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1.69 MB</t>
+        </is>
       </c>
       <c r="H31" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2705,11 +2705,13 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1.79 MB</t>
+        </is>
       </c>
       <c r="H32" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2775,11 +2775,13 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2.08 MB</t>
+        </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2845,14 +2845,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2.44 MB</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -2871,7 +2875,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2917,14 +2917,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2.06 MB</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -2943,7 +2947,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -2989,14 +2989,18 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2.00 MB</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -3015,7 +3019,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3061,14 +3061,18 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1.90 MB</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -3087,7 +3091,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3133,14 +3133,18 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2.54 MB</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -3159,7 +3163,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3205,14 +3205,18 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1.97 MB</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -3231,7 +3235,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3277,14 +3277,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2.49 MB</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -3303,7 +3307,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3349,14 +3349,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>3.69 MB</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -3375,7 +3379,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3421,14 +3421,18 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
+          <t>RECORDED_VERIFIED</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2.86 MB</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>180.000s (03:00)</t>
+        </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3451,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000s (03:00)</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3493,11 +3493,11 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>3058345</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3561,11 +3561,11 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>2857882</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3629,11 +3629,11 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
+        <v>2934181</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3697,11 +3697,11 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>2309033</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3765,11 +3765,11 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0</v>
+        <v>2805054</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3833,11 +3833,11 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0</v>
+        <v>2150216</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>0</v>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3894,21 +3894,21 @@
           <t>project_48_food_quality_freshness/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E49" s="2" t="n">
+        <v>2207148</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
+        <v>2207148</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -3927,17 +3927,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -3962,21 +3962,21 @@
           <t>project_49_healthcare_risk_assessment/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E50" s="2" t="n">
+        <v>1878820</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
+        <v>1878820</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -3995,17 +3995,17 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4030,21 +4030,21 @@
           <t>project_50_handwritten_document_recognition/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E51" s="2" t="n">
+        <v>2160352</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
+        <v>2160352</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4098,21 +4098,21 @@
           <t>project_51_energy_consumption_forecasting/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E52" s="2" t="n">
+        <v>2084985</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>2084985</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -4131,17 +4131,17 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4166,21 +4166,21 @@
           <t>project_52_crowd_density_estimation/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E53" s="2" t="n">
+        <v>2377419</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
+        <v>2377419</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -4199,17 +4199,17 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4234,21 +4234,21 @@
           <t>project_53_railway_track_defect_detection/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E54" s="2" t="n">
+        <v>1956829</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
+        <v>1956829</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -4267,17 +4267,17 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4302,21 +4302,21 @@
           <t>project_54_weather_event_prediction/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E55" s="2" t="n">
+        <v>2742955</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>0</v>
+        <v>2742955</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>

--- a/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
+++ b/AUDIT_MASTER/VIDEO_RECORDING_TRACKER.xlsx
@@ -4370,21 +4370,21 @@
           <t>project_55_accident_emergency_alert/walkthrough/walkthrough_video.mp4</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="E56" s="2" t="n">
+        <v>2274797</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
+        <v>2274797</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>180.000000</t>
+        </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -4403,17 +4403,17 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>02:30 - 03:30</t>
+          <t>180.000000</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL / TIER 1</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1. Start FastAPI backend (uvicorn app.main:app) &amp; frontend. 2. Ingest sensor/image input. 3. Trigger baseline &amp; deep model inference. 4. Verify SQLite audit trail &amp; metrics.</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
     </row>
